--- a/Shared/XLS/Reward.xlsx
+++ b/Shared/XLS/Reward.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="#Reward" sheetId="3" r:id="rId1"/>
+    <sheet name="#Enum" sheetId="4" r:id="rId1"/>
+    <sheet name="#Reward" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -30,56 +31,172 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Probability</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>MinCount</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>MaxCount</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!float</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
   </si>
   <si>
+    <t>Name</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>재료 보상1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>경험치 보상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!Enum</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardTypes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Equipment</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Experience</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!RewardTypes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>기초 재료 보상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 보상2</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 보상1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드 보상1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>경험치 보상1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화석 보상1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SourceIDs</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 장비 보상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>100001;100006;100011;200001;200006;200011;200016;200021;300001;300006;300011</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>30003;30004</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>매직 장비 보상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>100002;100007;100012;200002;200007;200012;200017;200022;300002;300007;300012</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화석 보상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드 보상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>Reward</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -120,8 +237,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -139,8 +263,14 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -181,45 +311,101 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="40% - 강조색3" xfId="1" builtinId="39"/>
@@ -501,7 +687,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -509,216 +695,467 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="21.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="12"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B18" s="12"/>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B19" s="12"/>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B20" s="12"/>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B21" s="12"/>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B22" s="12"/>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B23" s="12"/>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B24" s="12"/>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B25" s="12"/>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B26" s="12"/>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B27" s="12"/>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B28" s="12"/>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B29" s="12"/>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B30" s="12"/>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B31" s="12"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:U21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
-    <col min="2" max="2" width="13.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.625" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="2" max="6" width="13.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="78" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.625" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="J1" s="13"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" t="s">
         <v>3</v>
       </c>
-      <c r="F2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="7"/>
-      <c r="H2" s="6"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
+      <c r="J2" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="7"/>
+      <c r="L2" s="6"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
+      <c r="H3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
-        <v>101</v>
-      </c>
-      <c r="C4">
+        <v>10001</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4">
+        <v>90</v>
+      </c>
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
-      <c r="E4">
-        <v>500</v>
-      </c>
-      <c r="F4">
-        <v>1000</v>
-      </c>
-      <c r="G4" s="6"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="J4" s="14">
+        <v>10001</v>
+      </c>
+      <c r="K4" s="6"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
-        <v>102</v>
-      </c>
-      <c r="C5"/>
-      <c r="D5">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>3</v>
-      </c>
-      <c r="F5">
+        <v>10002</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
+        <v>90</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
         <v>5</v>
       </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
+      <c r="J5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="6"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
-        <v>103</v>
-      </c>
-      <c r="C6"/>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
+        <v>20001</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6">
+        <v>50</v>
+      </c>
+      <c r="H6">
         <v>1</v>
       </c>
-      <c r="F6">
+      <c r="I6">
         <v>1</v>
       </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
+      <c r="J6" s="15" t="s">
+        <v>30</v>
+      </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B7" s="1">
+        <v>20002</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7">
+        <v>30</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>33</v>
+      </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>30001</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <v>150</v>
+      </c>
+      <c r="I8">
+        <v>300</v>
+      </c>
+      <c r="J8" s="14"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C9" s="10"/>
-      <c r="D9"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>40001</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="7">
+        <v>100</v>
+      </c>
+      <c r="H9" s="8">
+        <v>500</v>
+      </c>
+      <c r="I9" s="8">
+        <v>2000</v>
+      </c>
+      <c r="K9"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C10" s="10"/>
-      <c r="D10"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="7"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C11" s="10"/>
-      <c r="D11"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G11"/>
+      <c r="J11" s="18"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G12"/>
+      <c r="J12" s="18"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G13"/>
+      <c r="J13" s="18"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+    </row>
+    <row r="18" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G18"/>
+      <c r="H18"/>
+    </row>
+    <row r="19" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G19"/>
+      <c r="H19"/>
+    </row>
+    <row r="20" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G20"/>
+      <c r="H20"/>
+    </row>
+    <row r="21" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G21"/>
+      <c r="H21"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Shared/XLS/Reward.xlsx
+++ b/Shared/XLS/Reward.xlsx
@@ -687,7 +687,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>

--- a/Shared/XLS/Reward.xlsx
+++ b/Shared/XLS/Reward.xlsx
@@ -4,11 +4,15 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="4" r:id="rId1"/>
-    <sheet name="#Reward" sheetId="3" r:id="rId2"/>
+    <sheet name="#RewardItem" sheetId="3" r:id="rId2"/>
+    <sheet name="#Reward_Eqiupment" sheetId="5" r:id="rId3"/>
+    <sheet name="#Reward_Material" sheetId="6" r:id="rId4"/>
+    <sheet name="#Reward_CardSkill" sheetId="8" r:id="rId5"/>
+    <sheet name="#Reward_Currency" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="145621"/>
   <extLst>
@@ -31,32 +35,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="78">
   <si>
     <t>!ID</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Probability</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>MinCount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxCount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>!int</t>
-  </si>
-  <si>
-    <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>!float</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -68,14 +53,6 @@
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>재료 보상1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>경험치 보상</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -95,10 +72,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Experience</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Icon</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -111,71 +84,293 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>기초 재료 보상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>RewardType</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>골드 보상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 상자</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 상자</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>다이아 상자</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드 상자</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 장비 보상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>고급 장비 보상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>다이아 보상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화석 재료 보상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화 재료</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>제작 재료</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>제작 재료 보상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Card_2_Blue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Card_2_Green</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Card_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Gem_Diamond_Blue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Coin_Gold</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Gem_Triangle_Green</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_GemStone_Red</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward_Eqiupment</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!ItemGradeTypes</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardItem</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>G</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rade</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardSourceID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>EquipmentSourceID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>W</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eight</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Material</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Currency</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialGrade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!MaterialGradeType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward_Material</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialSourceID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!MaterialType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enchant</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Craft</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward_Currency</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencySourceID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CurrencyInfo</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>Gold</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>장비 보상2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>장비 보상1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드 보상1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>경험치 보상1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>강화석 보상1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>SourceIDs</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반 장비 보상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>100001;100006;100011;200001;200006;200011;200016;200021;300001;300006;300011</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>30003;30004</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>매직 장비 보상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>100002;100007;100012;200002;200007;200012;200017;200022;300002;300007;300012</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>강화석 보상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드 보상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reward</t>
+    <t>Dia</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 스킬카드 보상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>고급 스킬카드 보상</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Currency</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward_CardSkill</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardSkillSourceID</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardGrade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CardSkillGrade</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Uncommon</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mythic</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -346,7 +541,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -404,6 +599,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -687,7 +888,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -695,7 +896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="9" bestFit="1" customWidth="1"/>
@@ -709,34 +910,31 @@
   <sheetData>
     <row r="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B17" s="12"/>
+        <v>49</v>
+      </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="12"/>
@@ -779,6 +977,9 @@
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B31" s="12"/>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B32" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -788,11 +989,615 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
-    <col min="2" max="6" width="13.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="78" style="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.625" customWidth="1"/>
+    <col min="24" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="L1" s="13"/>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A2" s="5"/>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="6"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A3" s="5"/>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="1">
+        <v>10001</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="1">
+        <v>10002</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2</v>
+      </c>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="1">
+        <v>20001</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="1">
+        <v>30001</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="1">
+        <v>40001</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="1">
+        <v>40002</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2</v>
+      </c>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="1">
+        <v>50001</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="1">
+        <v>60001</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2</v>
+      </c>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="6"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="6"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16" s="15"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+    </row>
+    <row r="17" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+      <c r="L17" s="15"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+    </row>
+    <row r="18" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+      <c r="L18" s="15"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+    </row>
+    <row r="19" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19" s="15"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+    </row>
+    <row r="20" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20" s="15"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+    </row>
+    <row r="21" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21" s="14"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+    </row>
+    <row r="22" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="I22" s="7"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="M22"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+    </row>
+    <row r="23" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="7"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+    </row>
+    <row r="24" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="I24"/>
+      <c r="L24" s="18"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+    </row>
+    <row r="25" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="I25"/>
+      <c r="L25" s="18"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+    </row>
+    <row r="26" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="I26"/>
+      <c r="L26" s="18"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1"/>
+    </row>
+    <row r="31" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="I31"/>
+      <c r="J31"/>
+    </row>
+    <row r="32" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="I32"/>
+      <c r="J32"/>
+    </row>
+    <row r="33" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="I33"/>
+      <c r="J33"/>
+    </row>
+    <row r="34" spans="9:23" x14ac:dyDescent="0.3">
+      <c r="I34"/>
+      <c r="J34"/>
+      <c r="L34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:U33"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="9"/>
+    <col min="2" max="2" width="13.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.375" style="1" bestFit="1" customWidth="1"/>
@@ -808,12 +1613,12 @@
   <sheetData>
     <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="4"/>
+        <v>33</v>
+      </c>
+      <c r="C1" s="20"/>
       <c r="D1" s="4"/>
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
@@ -825,29 +1630,18 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>2</v>
-      </c>
-      <c r="I2" t="s">
-        <v>3</v>
-      </c>
-      <c r="J2" s="19" t="s">
-        <v>28</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2" s="19"/>
       <c r="K2" s="7"/>
       <c r="L2" s="6"/>
       <c r="P2" s="1"/>
@@ -860,32 +1654,21 @@
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="5"/>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J3" s="19" t="s">
-        <v>4</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3" s="19"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
       <c r="P3" s="1"/>
@@ -896,206 +1679,1717 @@
       <c r="U3" s="1"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
       <c r="B4" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>27</v>
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="1">
+        <v>660000</v>
+      </c>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="1">
+        <v>280000</v>
+      </c>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="1">
+        <v>59000</v>
+      </c>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="1">
+        <v>648900</v>
+      </c>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="1">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="1">
+        <v>350000</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="1">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="1">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="1">
+        <v>100</v>
+      </c>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="6"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="6"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15" s="15"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16" s="15"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+    </row>
+    <row r="17" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17" s="15"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+    </row>
+    <row r="18" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18" s="15"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+    </row>
+    <row r="19" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19" s="15"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+    </row>
+    <row r="20" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20" s="14"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+    </row>
+    <row r="21" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G21" s="7"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="K21"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+    </row>
+    <row r="22" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="7"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+    </row>
+    <row r="23" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G23"/>
+      <c r="J23" s="18"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+    </row>
+    <row r="24" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G24"/>
+      <c r="J24" s="18"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+    </row>
+    <row r="25" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G25"/>
+      <c r="J25" s="18"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+    </row>
+    <row r="30" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G30"/>
+      <c r="H30"/>
+    </row>
+    <row r="31" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G31"/>
+      <c r="H31"/>
+    </row>
+    <row r="32" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G32"/>
+      <c r="H32"/>
+    </row>
+    <row r="33" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="9"/>
+      <c r="G33"/>
+      <c r="H33"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:V35"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="9"/>
+    <col min="2" max="2" width="13.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="78" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.625" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="K1" s="13"/>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" s="5"/>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="6"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" s="5"/>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4">
-        <v>90</v>
-      </c>
-      <c r="H4">
+        <v>59</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="1">
+        <v>659900</v>
+      </c>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="I4">
+      <c r="D5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="1">
+        <v>280000</v>
+      </c>
+      <c r="G5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="1">
         <v>3</v>
       </c>
-      <c r="J4" s="14">
-        <v>10001</v>
-      </c>
-      <c r="K4" s="6"/>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="1">
+        <v>59000</v>
+      </c>
+      <c r="G6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="1">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="1">
+        <v>800000</v>
+      </c>
+      <c r="I9" s="12"/>
+      <c r="J9"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="1">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="1">
+        <v>200000</v>
+      </c>
+      <c r="I10" s="12"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="I11" s="12"/>
+      <c r="J11"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="I12" s="12"/>
+      <c r="J12"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="I13" s="12"/>
+      <c r="J13"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="I14" s="12"/>
+      <c r="J14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="6"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="I15" s="12"/>
+      <c r="J15"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="6"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="E16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16"/>
+      <c r="K16" s="15"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="E17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17"/>
+      <c r="K17" s="15"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="E18" s="12"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18" s="15"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+      <c r="E19" s="12"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19" s="15"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20" s="15"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21" s="14"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="L22"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="7"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+      <c r="K24" s="18"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+      <c r="K25" s="18"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+      <c r="K26" s="18"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A31" s="5"/>
+      <c r="I31"/>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A32" s="5"/>
+      <c r="I32"/>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+      <c r="I33"/>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A34" s="5"/>
+      <c r="I34"/>
+      <c r="K34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:U33"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="9"/>
+    <col min="2" max="2" width="13.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="78" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.625" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="20"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="J1" s="13"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="5"/>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="6"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="5"/>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="1">
+        <v>660000</v>
+      </c>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="1">
+        <v>280000</v>
+      </c>
+      <c r="G5"/>
+      <c r="H5" s="7"/>
+      <c r="I5"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="1">
+        <v>59000</v>
+      </c>
+      <c r="G6"/>
+      <c r="H6" s="7"/>
+      <c r="I6"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G7"/>
+      <c r="I7"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="1">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="1">
+        <v>648900</v>
+      </c>
+      <c r="G8"/>
+      <c r="I8"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="1">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="1">
+        <v>350000</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="1">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G10"/>
+      <c r="I10"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="1">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="1">
+        <v>100</v>
+      </c>
+      <c r="G11"/>
+      <c r="H11" s="12"/>
+      <c r="I11"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="G12"/>
+      <c r="H12" s="12"/>
+      <c r="I12"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G13"/>
+      <c r="H13" s="12"/>
+      <c r="I13"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="6"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G14"/>
+      <c r="I14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="6"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G15"/>
+      <c r="I15"/>
+      <c r="J15" s="15"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G16"/>
+      <c r="I16"/>
+      <c r="J16" s="15"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+    </row>
+    <row r="17" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17" s="15"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+    </row>
+    <row r="18" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18" s="15"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+    </row>
+    <row r="19" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19" s="15"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+    </row>
+    <row r="20" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20" s="14"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+    </row>
+    <row r="21" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G21" s="7"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="K21"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+    </row>
+    <row r="22" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="17"/>
+      <c r="K22" s="7"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+    </row>
+    <row r="23" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G23"/>
+      <c r="J23" s="18"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+    </row>
+    <row r="24" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G24"/>
+      <c r="J24" s="18"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+    </row>
+    <row r="25" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G25"/>
+      <c r="J25" s="18"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+    </row>
+    <row r="30" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G30"/>
+      <c r="H30"/>
+    </row>
+    <row r="31" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G31"/>
+      <c r="H31"/>
+    </row>
+    <row r="32" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G32"/>
+      <c r="H32"/>
+    </row>
+    <row r="33" spans="7:21" x14ac:dyDescent="0.3">
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="J33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:T35"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9" style="9"/>
+    <col min="2" max="2" width="13.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="78" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.625" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="4"/>
+      <c r="I1" s="13"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" s="5"/>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="6"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="5"/>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3000</v>
+      </c>
+      <c r="F4" s="1">
+        <v>5000</v>
+      </c>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
       <c r="B5" s="1">
-        <v>10002</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>90</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" s="6"/>
+        <v>68</v>
+      </c>
+      <c r="E5" s="22">
+        <v>100</v>
+      </c>
+      <c r="F5" s="1">
+        <v>300</v>
+      </c>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B6" s="1">
-        <v>20001</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6">
-        <v>50</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>30</v>
-      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="E6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B7" s="1">
-        <v>20002</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7">
-        <v>30</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>33</v>
-      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B8" s="1">
-        <v>30001</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8">
-        <v>100</v>
-      </c>
-      <c r="H8">
-        <v>150</v>
-      </c>
-      <c r="I8">
-        <v>300</v>
-      </c>
-      <c r="J8" s="14"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B9" s="1">
-        <v>40001</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="7">
-        <v>100</v>
-      </c>
-      <c r="H9" s="8">
-        <v>500</v>
-      </c>
-      <c r="I9" s="8">
-        <v>2000</v>
-      </c>
-      <c r="K9"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="D9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="17"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -1103,60 +3397,258 @@
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="G11"/>
-      <c r="J11" s="18"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="G11" s="12"/>
+      <c r="H11"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="G12"/>
-      <c r="J12" s="18"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="G12" s="12"/>
+      <c r="H12"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="G13"/>
-      <c r="J13" s="18"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="G13" s="12"/>
+      <c r="H13"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
       <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-    </row>
-    <row r="18" spans="7:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="G14" s="12"/>
+      <c r="H14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="6"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="G15" s="12"/>
+      <c r="H15"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="6"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="G16" s="12"/>
+      <c r="H16"/>
+      <c r="I16" s="15"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="G17" s="12"/>
+      <c r="H17"/>
+      <c r="I17" s="15"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
       <c r="G18"/>
       <c r="H18"/>
-    </row>
-    <row r="19" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="I18" s="15"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
       <c r="G19"/>
       <c r="H19"/>
-    </row>
-    <row r="20" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="I19" s="15"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
       <c r="G20"/>
       <c r="H20"/>
-    </row>
-    <row r="21" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="I20" s="15"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
       <c r="G21"/>
       <c r="H21"/>
+      <c r="I21" s="14"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="J22"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="7"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+      <c r="I24" s="18"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+      <c r="I25" s="18"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+      <c r="I26" s="18"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A31" s="5"/>
+      <c r="G31"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A32" s="5"/>
+      <c r="G32"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+      <c r="G33"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A34" s="5"/>
+      <c r="G34"/>
+      <c r="I34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Reward.xlsx
+++ b/Shared/XLS/Reward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="4" r:id="rId1"/>
@@ -35,169 +35,169 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="79">
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RewardTypes</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Material</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Equipment</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Icon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!RewardTypes</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>RewardType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>골드 보상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>스킬 상자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>장비 상자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>다이아 상자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Skill</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>골드 상자</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>일반 장비 보상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>고급 장비 보상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>다이아 보상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>강화석 재료 보상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>강화 재료</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>제작 재료</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>제작 재료 보상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_Card_2_Blue</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_Card_2_Green</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_Card_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_Gem_Diamond_Blue</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_Coin_Gold</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_Gem_Triangle_Green</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_GemStone_Red</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Reward_Eqiupment</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!ItemGradeTypes</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Magic</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Rare</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Epic</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Legendary</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>RewardItem</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -214,23 +214,23 @@
       </rPr>
       <t>rade</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>RewardSourceID</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>EquipmentSourceID</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -247,143 +247,155 @@
       </rPr>
       <t>eight</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Material</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Currency</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>MaterialGrade</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward_Material</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialSourceID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enchant</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Craft</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward_Currency</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencySourceID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MinCount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxCount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dia</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 스킬카드 보상</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>고급 스킬카드 보상</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Currency</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward_CardSkill</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardSkillSourceID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardGrade</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CardSkillGrade</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Uncommon</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mythic</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>!MaterialType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!MaterialGradeType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rare</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Epic</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Legendary</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reward_Material</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaterialSourceID</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaterialType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>!MaterialType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enchant</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Craft</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reward_Currency</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>CurrencySourceID</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>CurrencyType</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>MinCount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxCount</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Currency</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>!CurrencyInfo</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gold</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dia</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반 스킬카드 보상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>고급 스킬카드 보상</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Currency</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reward_CardSkill</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>CardSkillSourceID</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>CardGrade</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>!CardSkillGrade</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Uncommon</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mythic</t>
-    <phoneticPr fontId="4" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -533,42 +545,42 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -577,7 +589,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -598,10 +610,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -888,7 +900,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -982,7 +994,7 @@
       <c r="B32" s="12"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1235,7 +1247,7 @@
         <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>28</v>
@@ -1268,7 +1280,7 @@
         <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>28</v>
@@ -1307,7 +1319,7 @@
         <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1340,7 +1352,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G11" s="1">
         <v>2</v>
@@ -1581,7 +1593,7 @@
       <c r="W34" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2093,7 +2105,7 @@
       <c r="H33"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2129,7 +2141,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -2144,10 +2156,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" t="s">
         <v>56</v>
-      </c>
-      <c r="D2" t="s">
-        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>50</v>
@@ -2177,10 +2189,10 @@
         <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="F3" s="21" t="s">
         <v>47</v>
@@ -2207,7 +2219,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>35</v>
@@ -2236,7 +2248,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>36</v>
@@ -2266,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>37</v>
@@ -2296,7 +2308,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>38</v>
@@ -2325,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>39</v>
@@ -2354,7 +2366,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>35</v>
@@ -2383,7 +2395,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>36</v>
@@ -2657,7 +2669,7 @@
       <c r="A35" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2691,7 +2703,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="4"/>
@@ -2705,10 +2717,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E2" s="21" t="s">
         <v>46</v>
@@ -2735,7 +2747,7 @@
         <v>44</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>47</v>
@@ -2762,7 +2774,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E4" s="1">
         <v>660000</v>
@@ -2789,7 +2801,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E5" s="1">
         <v>280000</v>
@@ -2816,7 +2828,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E6" s="1">
         <v>59000</v>
@@ -2843,7 +2855,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7" s="1">
         <v>1000</v>
@@ -2869,7 +2881,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" s="1">
         <v>648900</v>
@@ -2895,7 +2907,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" s="1">
         <v>350000</v>
@@ -2921,7 +2933,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" s="1">
         <v>1000</v>
@@ -2947,7 +2959,7 @@
         <v>2</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E11" s="1">
         <v>100</v>
@@ -3170,7 +3182,7 @@
       <c r="U33" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3203,7 +3215,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -3216,16 +3228,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -3248,7 +3260,7 @@
         <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>44</v>
@@ -3277,7 +3289,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E4" s="1">
         <v>3000</v>
@@ -3306,7 +3318,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E5" s="22">
         <v>100</v>
@@ -3648,7 +3660,7 @@
       <c r="A35" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Reward.xlsx
+++ b/Shared/XLS/Reward.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="4" r:id="rId1"/>
@@ -38,166 +38,158 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="79">
   <si>
     <t>!ID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!Table</t>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!Enum</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
     <t>RewardTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Material</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Equipment</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Icon</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!RewardTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Desc</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>RewardType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>골드 보상</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>스킬 상자</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>장비 상자</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>다이아 상자</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Skill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>골드 상자</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>일반 장비 보상</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>고급 장비 보상</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>다이아 보상</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>강화석 재료 보상</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>강화 재료</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>제작 재료</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>제작 재료 보상</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_Card_2_Blue</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_Card_2_Green</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_Card_1</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_Gem_Diamond_Blue</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_Coin_Gold</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_Gem_Triangle_Green</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_GemStone_Red</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reward_Eqiupment</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!ItemGradeTypes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Normal</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Magic</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Rare</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Epic</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Legendary</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>RewardItem</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -214,23 +206,23 @@
       </rPr>
       <t>rade</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>RewardSourceID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>EquipmentSourceID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -247,147 +239,163 @@
       </rPr>
       <t>eight</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Material</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Currency</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MaterialGrade</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Rare</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Epic</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Legendary</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Reward_Material</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MaterialSourceID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MaterialType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Enchant</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Craft</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Reward_Currency</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CurrencySourceID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MinCount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>MaxCount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Gold</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Dia</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>일반 스킬카드 보상</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>고급 스킬카드 보상</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward_CardSkill</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardSkillSourceID</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>CardGrade</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CardSkillGrade</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Uncommon</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mythic</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>!MaterialType</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>!MaterialGradeType</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Currency</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reward_CardSkill</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>CardSkillSourceID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>CardGrade</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!CardSkillGrade</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Uncommon</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mythic</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!MaterialType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!MaterialGradeType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CurrencyInfo</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>Currency</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>!CurrencyInfo</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardItem</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward_Eqiupment</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -545,42 +553,42 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -589,7 +597,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -610,13 +618,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -945,7 +956,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
@@ -994,7 +1005,7 @@
       <c r="B32" s="12"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1029,8 +1040,8 @@
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="20" t="s">
-        <v>40</v>
+      <c r="B1" s="23" t="s">
+        <v>77</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -1058,7 +1069,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I2"/>
       <c r="J2"/>
@@ -1091,7 +1102,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I3"/>
       <c r="J3"/>
@@ -1187,7 +1198,7 @@
         <v>32</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -1247,7 +1258,7 @@
         <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>28</v>
@@ -1280,7 +1291,7 @@
         <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>28</v>
@@ -1319,7 +1330,7 @@
         <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
@@ -1352,7 +1363,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G11" s="1">
         <v>2</v>
@@ -1593,7 +1604,7 @@
       <c r="W34" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1627,8 +1638,8 @@
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="20" t="s">
-        <v>33</v>
+      <c r="B1" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="4"/>
@@ -1642,13 +1653,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -1669,13 +1680,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
@@ -1699,7 +1710,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" s="1">
         <v>660000</v>
@@ -1726,7 +1737,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" s="1">
         <v>280000</v>
@@ -1753,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E6" s="1">
         <v>59000</v>
@@ -1780,7 +1791,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1">
         <v>1000</v>
@@ -1807,7 +1818,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" s="1">
         <v>648900</v>
@@ -1834,7 +1845,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E9" s="1">
         <v>350000</v>
@@ -1861,7 +1872,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E10" s="1">
         <v>1000</v>
@@ -1888,7 +1899,7 @@
         <v>2</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E11" s="1">
         <v>100</v>
@@ -2105,7 +2116,7 @@
       <c r="H33"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -2141,7 +2152,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -2156,16 +2167,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
@@ -2186,16 +2197,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
@@ -2219,10 +2230,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4" s="1">
         <v>659900</v>
@@ -2248,10 +2259,10 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F5" s="1">
         <v>280000</v>
@@ -2278,10 +2289,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" s="1">
         <v>59000</v>
@@ -2308,10 +2319,10 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" s="1">
         <v>1000</v>
@@ -2337,10 +2348,10 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8" s="1">
         <v>100</v>
@@ -2366,10 +2377,10 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1">
         <v>800000</v>
@@ -2395,10 +2406,10 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1">
         <v>200000</v>
@@ -2669,7 +2680,7 @@
       <c r="A35" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2703,7 +2714,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="4"/>
@@ -2717,13 +2728,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -2744,13 +2755,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
@@ -2774,7 +2785,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E4" s="1">
         <v>660000</v>
@@ -2801,7 +2812,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E5" s="1">
         <v>280000</v>
@@ -2828,7 +2839,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E6" s="1">
         <v>59000</v>
@@ -2855,7 +2866,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E7" s="1">
         <v>1000</v>
@@ -2881,7 +2892,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E8" s="1">
         <v>648900</v>
@@ -2907,7 +2918,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1">
         <v>350000</v>
@@ -2933,7 +2944,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" s="1">
         <v>1000</v>
@@ -2959,7 +2970,7 @@
         <v>2</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E11" s="1">
         <v>100</v>
@@ -3182,7 +3193,7 @@
       <c r="U33" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3215,7 +3226,7 @@
         <v>2</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C1" s="20"/>
       <c r="D1" s="20"/>
@@ -3228,16 +3239,16 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="G2"/>
       <c r="H2"/>
@@ -3257,16 +3268,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G3"/>
       <c r="H3"/>
@@ -3289,7 +3300,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E4" s="1">
         <v>3000</v>
@@ -3318,7 +3329,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E5" s="22">
         <v>100</v>
@@ -3660,7 +3671,7 @@
       <c r="A35" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>